--- a/data/scenarios/feed_dist/free_cattle_rations.xlsx
+++ b/data/scenarios/feed_dist/free_cattle_rations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Git repos\CIBUSmod\data\scenarios\feed_dist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0365BD29-F358-479E-B358-21B961DE2241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A17D6F9-7051-4346-958B-795F7D49FF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="2055" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
